--- a/experiment/ELAN_bestx3/Test/results-Set14/Set14.xlsx
+++ b/experiment/ELAN_bestx3/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.02</v>
+        <v>24.15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5632</v>
+        <v>0.6471</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.54</v>
+        <v>27.49</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7129</v>
+        <v>0.8205</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.05</v>
+        <v>26.87</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6778</v>
+        <v>0.7411</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.65</v>
+        <v>27.63</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6237</v>
+        <v>0.6874</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.83</v>
+        <v>25.73</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7239</v>
+        <v>0.8421</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.31</v>
+        <v>34.08</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7523</v>
+        <v>0.8357</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.85</v>
+        <v>30.73</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7789</v>
+        <v>0.8865</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.23</v>
+        <v>35.44</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8405</v>
+        <v>0.947</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28.93</v>
+        <v>34.46</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7814</v>
+        <v>0.8965</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.35</v>
+        <v>28.97</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7345</v>
+        <v>0.8185</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28.3</v>
+        <v>36.07</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8224</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.72</v>
+        <v>35.69</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7967</v>
+        <v>0.8999</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23.7</v>
+        <v>28.74</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8697</v>
+        <v>0.9705</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26.33</v>
+        <v>30.26</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7975</v>
+        <v>0.8631</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.42</v>
+        <v>30.45</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7482</v>
+        <v>0.8444</v>
       </c>
     </row>
   </sheetData>
